--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99366</v>
+        <v>99369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99369</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99375</v>
+        <v>99377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106367</v>
+        <v>106369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106369</v>
+        <v>106375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106375</v>
+        <v>106377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106377</v>
+        <v>106378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106378</v>
+        <v>106384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106384</v>
+        <v>106388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106388</v>
+        <v>106390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106390</v>
+        <v>106392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106392</v>
+        <v>106405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39946-2025 artfynd.xlsx
+++ b/artfynd/A 39946-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136546202</v>
       </c>
       <c r="B2" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136549730</v>
       </c>
       <c r="B3" t="n">
-        <v>106405</v>
+        <v>106407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
